--- a/recipes/onion-garlic-free-indian/focus-states/11-bihar/excel/bihar-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/11-bihar/excel/bihar-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kadhi Bari</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kadhi Bari</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Side  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -1728,36 +1731,215 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Simmer baris in kadhi. Tadka.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Simmer baris in kadhi. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Tadka. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 178  ·  Protein 10 g  ·  Carbs 25 g  ·  Fat 4 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Kadhi Bari: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1771,7 +1953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1783,7 +1965,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo Bhujiya</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo Bhujiya</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1793,7 +1975,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Side  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1813,44 +1995,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2034,36 +2216,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Fry until crisp-edged.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Fry until crisp-edged. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 142  ·  Protein 2 g  ·  Carbs 18 g  ·  Fat 7 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo Bhujiya: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2077,7 +2412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2089,7 +2424,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Nenua Sabzi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Nenua Sabzi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2099,7 +2434,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Side  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2119,44 +2454,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2340,36 +2675,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Simmer until soft.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Simmer until soft. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 131  ·  Protein 5 g  ·  Carbs 20 g  ·  Fat 4 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Nenua Sabzi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2383,7 +2884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2395,7 +2896,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sattu Paratha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sattu Paratha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2405,7 +2906,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Bread  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2425,44 +2926,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2592,33 +3093,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Stuff, cook on iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Stuff, cook on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 460  ·  Protein 16 g  ·  Carbs 76 g  ·  Fat 10 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Sattu Paratha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2632,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2644,7 +3298,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Phulka</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Phulka</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2654,7 +3308,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Bread  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2674,44 +3328,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2841,33 +3495,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 318  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Phulka: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2881,7 +3688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2893,7 +3700,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Litti as Bread</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Litti as Bread</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2903,7 +3710,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Bread  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2923,44 +3730,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 25 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -3072,32 +3879,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Roast, crush slightly, pour ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron grill or steel oven tray — never aluminium foil. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Roast, crush slightly, pour ghee. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 398  ·  Protein 16 g  ·  Carbs 76 g  ·  Fat 3 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Litti as Bread: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3111,7 +4071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3123,7 +4083,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Thekua</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Thekua</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3133,7 +4093,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Sweet  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3153,44 +4113,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3356,35 +4316,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Press, fry on low-medium.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Press, fry on low-medium. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 415  ·  Protein 9 g  ·  Carbs 79 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Thekua: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3398,7 +4511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3410,7 +4523,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Khaja</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Khaja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3420,7 +4533,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Sweet  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3440,44 +4553,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3607,33 +4720,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Layer, fry, dip in syrup.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Layer, fry, dip in syrup. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 532  ·  Protein 6 g  ·  Carbs 110 g  ·  Fat 8 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Khaja: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3647,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3659,7 +4925,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Anarsa</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Anarsa</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3669,7 +4935,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Sweet  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3689,44 +4955,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 40 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3874,34 +5140,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Shape, dip in poppy, fry on low.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Shape, dip in poppy, fry on low. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 254  ·  Protein 2 g  ·  Carbs 45 g  ·  Fat 7 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Anarsa: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3915,7 +5334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3927,7 +5346,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Lai Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Lai Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3937,7 +5356,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Dessert  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3957,44 +5376,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -4142,34 +5561,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Warm milk, soak lai.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Warm milk, soak lai. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 347  ·  Protein 10 g  ·  Carbs 57 g  ·  Fat 9 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Lai Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4447,7 +6019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4459,7 +6031,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chura Dahi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chura Dahi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4469,7 +6041,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Dessert  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4489,44 +6061,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>Prep 5 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4674,34 +6246,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Soak chura, mix yogurt and jaggery.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Soak chura, mix yogurt and jaggery. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 311  ·  Protein 5 g  ·  Carbs 70 g  ·  Fat 2 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Chura Dahi: keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4715,7 +6440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4727,7 +6452,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rasiyaw</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rasiyaw</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4737,7 +6462,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Dessert  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4757,44 +6482,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -4942,34 +6667,200 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel. Jaggery off the hard boil.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Jaggery off the hard boil. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 436  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 9 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Rasiyaw: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4983,7 +6874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4995,7 +6886,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Cucumber Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Cucumber Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5005,7 +6896,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Salad  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5025,44 +6916,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5246,36 +7137,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Toss. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>No onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 87  ·  Protein 1 g  ·  Carbs 6 g  ·  Fat 7 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Cucumber Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5289,7 +7346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5301,7 +7358,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kachumber without Onion</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kachumber without Onion</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5311,7 +7368,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Salad  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5331,44 +7388,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5534,35 +7591,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 24  ·  Protein 1 g  ·  Carbs 6 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Kachumber without Onion: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5576,7 +7786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5588,7 +7798,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chana Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chana Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5598,7 +7808,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Salad  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5618,44 +7828,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5857,37 +8067,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Toss. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>No onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 679  ·  Protein 1 g  ·  Carbs 3 g  ·  Fat 75 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Chana Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8964,7 +11340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8976,7 +11352,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Baked Sattu Litti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Baked Sattu Litti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8986,7 +11362,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Starter  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9006,44 +11382,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 25 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -9245,37 +11621,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Stuff, roast on steel tray until charred spots. Dip in ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron grill or steel oven tray — never aluminium foil. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="66" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Stuff, roast on steel tray until charred spots. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Dip in ghee. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 462  ·  Protein 17 g  ·  Carbs 77 g  ·  Fat 10 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Baked Sattu Litti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9289,7 +11831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9301,7 +11843,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sattu Cooler Chaat</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sattu Cooler Chaat</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9311,7 +11853,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Starter  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9331,44 +11873,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -9570,37 +12112,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Whisk a thick cooler. Top with chilli and cumin.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Whisk a thick cooler. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Top with chilli and cumin. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 148  ·  Protein 8 g  ·  Carbs 24 g  ·  Fat 2 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Sattu Cooler Chaat: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9614,7 +12322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9626,7 +12334,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo Chop (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo Chop (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9636,7 +12344,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Starter  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9656,44 +12364,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9859,35 +12567,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Shape, fry in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Shape, fry in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 286  ·  Protein 10 g  ·  Carbs 39 g  ·  Fat 9 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo Chop (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9901,7 +12762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9913,7 +12774,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Litti with Tomato Baingan Chokha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Litti with Tomato Baingan Chokha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9923,7 +12784,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Main  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9943,44 +12804,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -10182,37 +13043,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Roast, peel, mash. Serve with litti.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron grill or steel oven tray — never aluminium foil. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Roast, peel, mash. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve with litti. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 160  ·  Protein 3 g  ·  Carbs 22 g  ·  Fat 8 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Litti with Tomato Baingan Chokha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10226,7 +13253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10238,7 +13265,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ghugni</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ghugni</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10248,7 +13275,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Main  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10268,44 +13295,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10543,39 +13570,231 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Cook peas soft. Tomato-ginger gravy. Simmer.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Cook peas soft. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Tomato-ginger gravy. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Simmer. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 58  ·  Protein 3 g  ·  Carbs 11 g  ·  Fat 0 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Ghugni: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="35">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10589,7 +13808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10601,7 +13820,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dal Pithaur</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dal Pithaur</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10611,7 +13830,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Bihar kitchen  ·  Main  ·  Magadh vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Bihar  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10631,44 +13850,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 20 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10870,37 +14089,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Simmer pithaur in dal until cooked. Tadka.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Simmer pithaur in dal until cooked. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Tadka. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 449  ·  Protein 17 g  ·  Carbs 78 g  ·  Fat 9 g  ·  Fibre 14 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Dal Pithaur: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
